--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/31.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/31.xlsx
@@ -426,13 +426,13 @@
         <v>-8.717153420704461</v>
       </c>
       <c r="E2">
-        <v>-13.26020268190981</v>
+        <v>-25.33484879190392</v>
       </c>
       <c r="F2">
-        <v>-3.259497480316128</v>
+        <v>-5.579980719858508</v>
       </c>
       <c r="G2">
-        <v>-6.433260319511009</v>
+        <v>-14.80481314825418</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.862397716711685</v>
       </c>
       <c r="E3">
-        <v>-15.07182776562635</v>
+        <v>-25.46770969081496</v>
       </c>
       <c r="F3">
-        <v>-3.228050168603651</v>
+        <v>-6.149050901498907</v>
       </c>
       <c r="G3">
-        <v>-6.943929955693628</v>
+        <v>-14.35211613458383</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.992021026119989</v>
       </c>
       <c r="E4">
-        <v>-14.52633231513639</v>
+        <v>-27.25328246356538</v>
       </c>
       <c r="F4">
-        <v>-3.226160662557865</v>
+        <v>-5.478369860761509</v>
       </c>
       <c r="G4">
-        <v>-6.963961813314038</v>
+        <v>-14.57805120750252</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.065230307741214</v>
       </c>
       <c r="E5">
-        <v>-14.86388929614215</v>
+        <v>-27.31899514989068</v>
       </c>
       <c r="F5">
-        <v>-3.01034610310651</v>
+        <v>-5.406054214864516</v>
       </c>
       <c r="G5">
-        <v>-6.415695940503301</v>
+        <v>-14.77059656983229</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.100725391729865</v>
       </c>
       <c r="E6">
-        <v>-15.70883461886332</v>
+        <v>-26.67590202758741</v>
       </c>
       <c r="F6">
-        <v>-2.991282055698482</v>
+        <v>-5.618555304704673</v>
       </c>
       <c r="G6">
-        <v>-6.440738223444984</v>
+        <v>-14.29954768397997</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.092044206444752</v>
       </c>
       <c r="E7">
-        <v>-16.48888690905458</v>
+        <v>-28.33436053494252</v>
       </c>
       <c r="F7">
-        <v>-3.094525626946398</v>
+        <v>-4.807648230021375</v>
       </c>
       <c r="G7">
-        <v>-5.657034860079411</v>
+        <v>-14.89729929973947</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.063063991532211</v>
       </c>
       <c r="E8">
-        <v>-16.30807852735032</v>
+        <v>-30.00598105200092</v>
       </c>
       <c r="F8">
-        <v>-2.756368657408181</v>
+        <v>-5.374333541909114</v>
       </c>
       <c r="G8">
-        <v>-6.595008136283837</v>
+        <v>-14.80178294014404</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.012136164969109</v>
       </c>
       <c r="E9">
-        <v>-17.39536966506599</v>
+        <v>-31.23240728936524</v>
       </c>
       <c r="F9">
-        <v>-2.862078278414232</v>
+        <v>-5.358851355150791</v>
       </c>
       <c r="G9">
-        <v>-6.025768695265129</v>
+        <v>-14.18053941862969</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.959704200851872</v>
       </c>
       <c r="E10">
-        <v>-18.27370342664571</v>
+        <v>-30.02972157698613</v>
       </c>
       <c r="F10">
-        <v>-2.858310035098897</v>
+        <v>-5.466900285702347</v>
       </c>
       <c r="G10">
-        <v>-5.860952936334221</v>
+        <v>-13.75628403343661</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.899726572773226</v>
       </c>
       <c r="E11">
-        <v>-18.88469419670861</v>
+        <v>-31.25776447957119</v>
       </c>
       <c r="F11">
-        <v>-2.536232505216421</v>
+        <v>-4.584924258063269</v>
       </c>
       <c r="G11">
-        <v>-5.689991449422473</v>
+        <v>-14.22426825835241</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.847352409640944</v>
       </c>
       <c r="E12">
-        <v>-18.71077815244403</v>
+        <v>-30.99910936543808</v>
       </c>
       <c r="F12">
-        <v>-2.414549475582188</v>
+        <v>-4.984257817033035</v>
       </c>
       <c r="G12">
-        <v>-4.254817951536949</v>
+        <v>-13.2066728597865</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.79535525233729</v>
       </c>
       <c r="E13">
-        <v>-18.8956712177032</v>
+        <v>-29.49227322480779</v>
       </c>
       <c r="F13">
-        <v>-2.499175489452186</v>
+        <v>-4.571503877770514</v>
       </c>
       <c r="G13">
-        <v>-4.758951394373154</v>
+        <v>-12.02664058792028</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.760229648112359</v>
       </c>
       <c r="E14">
-        <v>-21.33629228413714</v>
+        <v>-32.70478400703416</v>
       </c>
       <c r="F14">
-        <v>-2.30313571664046</v>
+        <v>-4.499607385779337</v>
       </c>
       <c r="G14">
-        <v>-3.707405196331668</v>
+        <v>-12.60779086319977</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.736976276151459</v>
       </c>
       <c r="E15">
-        <v>-21.04344945548312</v>
+        <v>-32.6601128751855</v>
       </c>
       <c r="F15">
-        <v>-2.001907365919045</v>
+        <v>-4.42462191174312</v>
       </c>
       <c r="G15">
-        <v>-3.992812410015288</v>
+        <v>-11.61061778761984</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.739444072973892</v>
       </c>
       <c r="E16">
-        <v>-22.17857939261581</v>
+        <v>-32.14277547607523</v>
       </c>
       <c r="F16">
-        <v>-1.324629207185752</v>
+        <v>-4.888567299763845</v>
       </c>
       <c r="G16">
-        <v>-3.807462766565375</v>
+        <v>-11.0880077861824</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.755111023767691</v>
       </c>
       <c r="E17">
-        <v>-22.39584199008182</v>
+        <v>-32.70863094570368</v>
       </c>
       <c r="F17">
-        <v>-1.605745625734598</v>
+        <v>-4.130253271484287</v>
       </c>
       <c r="G17">
-        <v>-3.168231588462153</v>
+        <v>-11.61495884374298</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.784935446975778</v>
       </c>
       <c r="E18">
-        <v>-23.31399462361099</v>
+        <v>-34.49825217421695</v>
       </c>
       <c r="F18">
-        <v>-1.104592459082328</v>
+        <v>-3.243652468635379</v>
       </c>
       <c r="G18">
-        <v>-3.248342612835996</v>
+        <v>-10.70591609802818</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.805063915273845</v>
       </c>
       <c r="E19">
-        <v>-24.54676751729707</v>
+        <v>-35.68299154410367</v>
       </c>
       <c r="F19">
-        <v>-1.013134899241443</v>
+        <v>-3.96951354717546</v>
       </c>
       <c r="G19">
-        <v>-1.772462280284</v>
+        <v>-9.621935024871586</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.80927602894424</v>
       </c>
       <c r="E20">
-        <v>-25.31333854036749</v>
+        <v>-35.36917282384612</v>
       </c>
       <c r="F20">
-        <v>-0.3739823502219978</v>
+        <v>-3.85571409011367</v>
       </c>
       <c r="G20">
-        <v>-2.857936309250145</v>
+        <v>-11.99786427484395</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.775943300947469</v>
       </c>
       <c r="E21">
-        <v>-25.12454645898771</v>
+        <v>-35.10823762305015</v>
       </c>
       <c r="F21">
-        <v>-0.1990013335242414</v>
+        <v>-3.249208328805956</v>
       </c>
       <c r="G21">
-        <v>-2.861847525349003</v>
+        <v>-10.50735953780151</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.707634843517132</v>
       </c>
       <c r="E22">
-        <v>-26.10411425700891</v>
+        <v>-33.53976215846446</v>
       </c>
       <c r="F22">
-        <v>0.0575506780619879</v>
+        <v>-3.514301636682451</v>
       </c>
       <c r="G22">
-        <v>-3.184207856235089</v>
+        <v>-10.81342532242339</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.59751032635206</v>
       </c>
       <c r="E23">
-        <v>-26.89765687126902</v>
+        <v>-36.17150520615512</v>
       </c>
       <c r="F23">
-        <v>0.2014993951160692</v>
+        <v>-3.379446736976302</v>
       </c>
       <c r="G23">
-        <v>-2.967276455275521</v>
+        <v>-11.68783477457825</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.463052545850275</v>
       </c>
       <c r="E24">
-        <v>-26.67768624634643</v>
+        <v>-37.06649243089805</v>
       </c>
       <c r="F24">
-        <v>0.4023470123336429</v>
+        <v>-2.729767295002081</v>
       </c>
       <c r="G24">
-        <v>-2.969606122582726</v>
+        <v>-10.81960386261982</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.310844835129254</v>
       </c>
       <c r="E25">
-        <v>-27.50566790543487</v>
+        <v>-35.29328012795158</v>
       </c>
       <c r="F25">
-        <v>0.5959281906938594</v>
+        <v>-3.351697257349922</v>
       </c>
       <c r="G25">
-        <v>-3.361410226552901</v>
+        <v>-9.697114373241584</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.164053737870875</v>
       </c>
       <c r="E26">
-        <v>-26.89840406948028</v>
+        <v>-36.84249825681965</v>
       </c>
       <c r="F26">
-        <v>1.016967460719181</v>
+        <v>-2.853436749668227</v>
       </c>
       <c r="G26">
-        <v>-3.014526045731525</v>
+        <v>-10.44323134364372</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.029117820881563</v>
       </c>
       <c r="E27">
-        <v>-28.00977763196873</v>
+        <v>-35.59688713932183</v>
       </c>
       <c r="F27">
-        <v>1.016844862343567</v>
+        <v>-2.229390308606234</v>
       </c>
       <c r="G27">
-        <v>-3.248352456500674</v>
+        <v>-11.34780834681612</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.92369519356097</v>
       </c>
       <c r="E28">
-        <v>-26.83611038103077</v>
+        <v>-35.10600508536437</v>
       </c>
       <c r="F28">
-        <v>0.7151418571003474</v>
+        <v>-1.910038935846371</v>
       </c>
       <c r="G28">
-        <v>-3.762011285523947</v>
+        <v>-12.07329299605246</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.847439953630606</v>
       </c>
       <c r="E29">
-        <v>-26.82327668569303</v>
+        <v>-35.30324956347946</v>
       </c>
       <c r="F29">
-        <v>0.7784258132046185</v>
+        <v>-3.245074775465986</v>
       </c>
       <c r="G29">
-        <v>-3.844478226977471</v>
+        <v>-12.4254468186983</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.807750755575122</v>
       </c>
       <c r="E30">
-        <v>-25.79026383743331</v>
+        <v>-36.96568859948732</v>
       </c>
       <c r="F30">
-        <v>0.7605678687350668</v>
+        <v>-3.103023019764316</v>
       </c>
       <c r="G30">
-        <v>-3.854554858386526</v>
+        <v>-11.96699782363425</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.79288484127976</v>
       </c>
       <c r="E31">
-        <v>-26.68789795523373</v>
+        <v>-35.70414178195649</v>
       </c>
       <c r="F31">
-        <v>0.954306436901815</v>
+        <v>-2.479170416674577</v>
       </c>
       <c r="G31">
-        <v>-3.55351918641527</v>
+        <v>-10.28529958754453</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.798393334754705</v>
       </c>
       <c r="E32">
-        <v>-25.73180576646829</v>
+        <v>-35.0566696252878</v>
       </c>
       <c r="F32">
-        <v>0.510504459014966</v>
+        <v>-2.493070421693553</v>
       </c>
       <c r="G32">
-        <v>-3.285564790206337</v>
+        <v>-11.46145673674904</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.803877799012096</v>
       </c>
       <c r="E33">
-        <v>-25.91835625321427</v>
+        <v>-34.71745522279524</v>
       </c>
       <c r="F33">
-        <v>0.6101363483866765</v>
+        <v>-2.660748551368229</v>
       </c>
       <c r="G33">
-        <v>-4.005353238815486</v>
+        <v>-11.44951965271578</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.797836349232579</v>
       </c>
       <c r="E34">
-        <v>-25.27416724020114</v>
+        <v>-33.52292982057794</v>
       </c>
       <c r="F34">
-        <v>0.6662507846197178</v>
+        <v>-2.100595744818967</v>
       </c>
       <c r="G34">
-        <v>-3.589314032407253</v>
+        <v>-10.9594462442618</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.758396866373717</v>
       </c>
       <c r="E35">
-        <v>-24.64701434640487</v>
+        <v>-34.47020280621344</v>
       </c>
       <c r="F35">
-        <v>0.7482185674941317</v>
+        <v>-3.532618496693154</v>
       </c>
       <c r="G35">
-        <v>-3.543570522647034</v>
+        <v>-11.07083715376183</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.676898166571291</v>
       </c>
       <c r="E36">
-        <v>-23.89578579327243</v>
+        <v>-33.50520763754893</v>
       </c>
       <c r="F36">
-        <v>0.4867609641485238</v>
+        <v>-3.464779348240888</v>
       </c>
       <c r="G36">
-        <v>-3.05993487089268</v>
+        <v>-10.5361227259916</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.539954005145063</v>
       </c>
       <c r="E37">
-        <v>-24.63898083351526</v>
+        <v>-36.01885487583056</v>
       </c>
       <c r="F37">
-        <v>0.4626753535447253</v>
+        <v>-3.383681351139414</v>
       </c>
       <c r="G37">
-        <v>-3.160976807594221</v>
+        <v>-12.42529916372813</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.349936670966099</v>
       </c>
       <c r="E38">
-        <v>-23.01489797235238</v>
+        <v>-32.68157331350785</v>
       </c>
       <c r="F38">
-        <v>0.5717614000845866</v>
+        <v>-3.990268292452602</v>
       </c>
       <c r="G38">
-        <v>-3.06194297848706</v>
+        <v>-12.13466824532187</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.106927585595509</v>
       </c>
       <c r="E39">
-        <v>-22.37746544255869</v>
+        <v>-32.91185527374591</v>
       </c>
       <c r="F39">
-        <v>0.03871940189414674</v>
+        <v>-3.558003815751944</v>
       </c>
       <c r="G39">
-        <v>-3.392529331822675</v>
+        <v>-11.38917142579448</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.824436819238211</v>
       </c>
       <c r="E40">
-        <v>-22.83338767717693</v>
+        <v>-31.89087684516156</v>
       </c>
       <c r="F40">
-        <v>0.5055193439849185</v>
+        <v>-2.933423077715145</v>
       </c>
       <c r="G40">
-        <v>-2.016844380809883</v>
+        <v>-11.53651139869978</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.511627412457088</v>
       </c>
       <c r="E41">
-        <v>-21.72516140412381</v>
+        <v>-30.8618558467396</v>
       </c>
       <c r="F41">
-        <v>-0.06245490758157648</v>
+        <v>-3.143322265543109</v>
       </c>
       <c r="G41">
-        <v>-2.198194215178833</v>
+        <v>-11.41297996942981</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.186687682949965</v>
       </c>
       <c r="E42">
-        <v>-21.69751959878099</v>
+        <v>-31.71905522012553</v>
       </c>
       <c r="F42">
-        <v>0.328572611440319</v>
+        <v>-2.509757054655546</v>
       </c>
       <c r="G42">
-        <v>-1.952991809263089</v>
+        <v>-10.31854820560638</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.860223513608473</v>
       </c>
       <c r="E43">
-        <v>-20.48424178569794</v>
+        <v>-31.23323147163464</v>
       </c>
       <c r="F43">
-        <v>-0.08015711897940191</v>
+        <v>-3.585712705375588</v>
       </c>
       <c r="G43">
-        <v>-1.346238162155251</v>
+        <v>-11.04389504353723</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.547979416593661</v>
       </c>
       <c r="E44">
-        <v>-20.97916323847024</v>
+        <v>-30.45588720889997</v>
       </c>
       <c r="F44">
-        <v>-0.2042084510182391</v>
+        <v>-3.367069271243672</v>
       </c>
       <c r="G44">
-        <v>-1.189113586559681</v>
+        <v>-10.85172702168679</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.257378132704253</v>
       </c>
       <c r="E45">
-        <v>-20.55591847229134</v>
+        <v>-31.01793423188797</v>
       </c>
       <c r="F45">
-        <v>-0.13968525727938</v>
+        <v>-3.29318883932279</v>
       </c>
       <c r="G45">
-        <v>-2.0329354913374</v>
+        <v>-13.15696891560403</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.999919331439672</v>
       </c>
       <c r="E46">
-        <v>-19.02715546051591</v>
+        <v>-31.21666631371458</v>
       </c>
       <c r="F46">
-        <v>0.230268595015296</v>
+        <v>-3.271020899256472</v>
       </c>
       <c r="G46">
-        <v>-1.420803922093632</v>
+        <v>-10.97888420077995</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.778687492923662</v>
       </c>
       <c r="E47">
-        <v>-19.28348973172009</v>
+        <v>-29.76867995705097</v>
       </c>
       <c r="F47">
-        <v>0.02249665467772122</v>
+        <v>-2.519051336914957</v>
       </c>
       <c r="G47">
-        <v>-1.438214083688045</v>
+        <v>-10.58056687201428</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.598651963163898</v>
       </c>
       <c r="E48">
-        <v>-17.96842993684064</v>
+        <v>-30.38503244033896</v>
       </c>
       <c r="F48">
-        <v>-0.1705212338485916</v>
+        <v>-2.475092363950596</v>
       </c>
       <c r="G48">
-        <v>-1.646758682341673</v>
+        <v>-10.75583332161202</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.456974575840142</v>
       </c>
       <c r="E49">
-        <v>-17.84252930247938</v>
+        <v>-30.11921780879972</v>
       </c>
       <c r="F49">
-        <v>0.2084112927250283</v>
+        <v>-3.571145864597359</v>
       </c>
       <c r="G49">
-        <v>-1.258399861008916</v>
+        <v>-10.17918816353364</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.352142114487235</v>
       </c>
       <c r="E50">
-        <v>-17.00984255889697</v>
+        <v>-29.94629576457982</v>
       </c>
       <c r="F50">
-        <v>-0.221772325059797</v>
+        <v>-3.374602444404731</v>
       </c>
       <c r="G50">
-        <v>-1.355245115335926</v>
+        <v>-11.98101848335776</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.277833285493452</v>
       </c>
       <c r="E51">
-        <v>-16.95384797779213</v>
+        <v>-27.91126973687988</v>
       </c>
       <c r="F51">
-        <v>-0.1565839522964899</v>
+        <v>-3.601426006639291</v>
       </c>
       <c r="G51">
-        <v>-1.099700299064813</v>
+        <v>-11.15712999955366</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.229996432599188</v>
       </c>
       <c r="E52">
-        <v>-16.96526426076547</v>
+        <v>-27.08073401845111</v>
       </c>
       <c r="F52">
-        <v>-0.04207706947270864</v>
+        <v>-3.55886945968787</v>
       </c>
       <c r="G52">
-        <v>-1.067360579374925</v>
+        <v>-9.849386022150735</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.202808508440386</v>
       </c>
       <c r="E53">
-        <v>-14.8794491328325</v>
+        <v>-27.7022263197378</v>
       </c>
       <c r="F53">
-        <v>-0.1002690511519711</v>
+        <v>-2.964358458372693</v>
       </c>
       <c r="G53">
-        <v>-1.363533480995084</v>
+        <v>-11.5381520094795</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.192756300691317</v>
       </c>
       <c r="E54">
-        <v>-15.07599396171341</v>
+        <v>-25.88370437010758</v>
       </c>
       <c r="F54">
-        <v>-0.2614834299826025</v>
+        <v>-3.033497315279951</v>
       </c>
       <c r="G54">
-        <v>-1.532106238611556</v>
+        <v>-10.89296213302433</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.197010425805884</v>
       </c>
       <c r="E55">
-        <v>-14.35503825732225</v>
+        <v>-27.60087907144614</v>
       </c>
       <c r="F55">
-        <v>0.05164027664301343</v>
+        <v>-3.636032711626047</v>
       </c>
       <c r="G55">
-        <v>-1.519289787200365</v>
+        <v>-10.76734056562099</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.214076518004549</v>
       </c>
       <c r="E56">
-        <v>-14.14071011101322</v>
+        <v>-26.36440641449579</v>
       </c>
       <c r="F56">
-        <v>-0.1253892926418661</v>
+        <v>-3.563105730585786</v>
       </c>
       <c r="G56">
-        <v>-1.636724706812891</v>
+        <v>-11.38060415630276</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.244953008721252</v>
       </c>
       <c r="E57">
-        <v>-13.87723443629895</v>
+        <v>-25.32067919673392</v>
       </c>
       <c r="F57">
-        <v>-0.04273065135351745</v>
+        <v>-2.886029693498777</v>
       </c>
       <c r="G57">
-        <v>-2.225533353212127</v>
+        <v>-11.728777857197</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.290388131487314</v>
       </c>
       <c r="E58">
-        <v>-13.73584642083146</v>
+        <v>-26.09257570523737</v>
       </c>
       <c r="F58">
-        <v>-0.1102359677424548</v>
+        <v>-3.493338142819804</v>
       </c>
       <c r="G58">
-        <v>-2.053564531281629</v>
+        <v>-11.44901106337407</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.354465384477492</v>
       </c>
       <c r="E59">
-        <v>-12.59450794583425</v>
+        <v>-25.44200607234743</v>
       </c>
       <c r="F59">
-        <v>0.1441084447153138</v>
+        <v>-3.643531093356188</v>
       </c>
       <c r="G59">
-        <v>-2.660288647395433</v>
+        <v>-11.86841352188073</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.439039584542013</v>
       </c>
       <c r="E60">
-        <v>-12.89047995002757</v>
+        <v>-25.37825421526744</v>
       </c>
       <c r="F60">
-        <v>0.1051453555572363</v>
+        <v>-2.962922069296238</v>
       </c>
       <c r="G60">
-        <v>-3.049520273663003</v>
+        <v>-13.08255737307894</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.549705401404649</v>
       </c>
       <c r="E61">
-        <v>-12.2091302793075</v>
+        <v>-23.84196035121726</v>
       </c>
       <c r="F61">
-        <v>0.1048587404358677</v>
+        <v>-3.238606054417525</v>
       </c>
       <c r="G61">
-        <v>-2.895204423722318</v>
+        <v>-12.98725429288487</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.68710120464737</v>
       </c>
       <c r="E62">
-        <v>-12.01269413380277</v>
+        <v>-24.98056362791383</v>
       </c>
       <c r="F62">
-        <v>-0.1339935448547446</v>
+        <v>-2.499324595584689</v>
       </c>
       <c r="G62">
-        <v>-2.774442345448514</v>
+        <v>-13.14712196970414</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.855072557172844</v>
       </c>
       <c r="E63">
-        <v>-11.5035623295944</v>
+        <v>-24.80187004357116</v>
       </c>
       <c r="F63">
-        <v>-0.2674228242606749</v>
+        <v>-3.220619713000539</v>
       </c>
       <c r="G63">
-        <v>-2.742082938429271</v>
+        <v>-12.29468685833287</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.049813322163316</v>
       </c>
       <c r="E64">
-        <v>-12.37979035076056</v>
+        <v>-23.81918665543268</v>
       </c>
       <c r="F64">
-        <v>-0.4672730871252781</v>
+        <v>-3.566203824672256</v>
       </c>
       <c r="G64">
-        <v>-3.978368472710613</v>
+        <v>-13.24178521169412</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.270852054897304</v>
       </c>
       <c r="E65">
-        <v>-11.47482010506772</v>
+        <v>-22.24046551840464</v>
       </c>
       <c r="F65">
-        <v>-0.00962163463102401</v>
+        <v>-3.705778761839556</v>
       </c>
       <c r="G65">
-        <v>-3.523522258918827</v>
+        <v>-13.58023337188616</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.509168312650692</v>
       </c>
       <c r="E66">
-        <v>-11.92741843976433</v>
+        <v>-22.99307978458342</v>
       </c>
       <c r="F66">
-        <v>-0.302533176628332</v>
+        <v>-3.296563608121795</v>
       </c>
       <c r="G66">
-        <v>-3.516949972135259</v>
+        <v>-13.38333054732544</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.760743944692281</v>
       </c>
       <c r="E67">
-        <v>-11.32005497738158</v>
+        <v>-24.20573719672743</v>
       </c>
       <c r="F67">
-        <v>-0.5848407875024035</v>
+        <v>-3.696320462834392</v>
       </c>
       <c r="G67">
-        <v>-3.662790426787898</v>
+        <v>-11.66916790512657</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.01301695599275</v>
       </c>
       <c r="E68">
-        <v>-11.66104454168515</v>
+        <v>-24.87802086248415</v>
       </c>
       <c r="F68">
-        <v>-0.4916138348891387</v>
+        <v>-3.70841628365007</v>
       </c>
       <c r="G68">
-        <v>-3.752840271265299</v>
+        <v>-13.02557896069919</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.260604432075813</v>
       </c>
       <c r="E69">
-        <v>-10.78881969154177</v>
+        <v>-23.26129224310972</v>
       </c>
       <c r="F69">
-        <v>-0.5863931480152498</v>
+        <v>-3.940014555594367</v>
       </c>
       <c r="G69">
-        <v>-4.238946682853915</v>
+        <v>-13.20128509398589</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.490898465217113</v>
       </c>
       <c r="E70">
-        <v>-11.11256482682413</v>
+        <v>-22.11484564943186</v>
       </c>
       <c r="F70">
-        <v>-0.6784388487121225</v>
+        <v>-4.120384102247335</v>
       </c>
       <c r="G70">
-        <v>-3.715746061535777</v>
+        <v>-14.2187426812463</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.700611398082025</v>
       </c>
       <c r="E71">
-        <v>-11.21804204341079</v>
+        <v>-24.92005868669735</v>
       </c>
       <c r="F71">
-        <v>-0.7406343300491149</v>
+        <v>-4.388305456436987</v>
       </c>
       <c r="G71">
-        <v>-4.182460453708074</v>
+        <v>-12.41050413571659</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.879797058079637</v>
       </c>
       <c r="E72">
-        <v>-11.03799897381383</v>
+        <v>-26.06719360842437</v>
       </c>
       <c r="F72">
-        <v>-1.045633409188073</v>
+        <v>-4.625814129800258</v>
       </c>
       <c r="G72">
-        <v>-3.89902525418168</v>
+        <v>-12.7254193748843</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.028369680688636</v>
       </c>
       <c r="E73">
-        <v>-11.99426777306556</v>
+        <v>-24.25535568642947</v>
       </c>
       <c r="F73">
-        <v>-1.137528347017636</v>
+        <v>-3.93094310416631</v>
       </c>
       <c r="G73">
-        <v>-4.658250704713796</v>
+        <v>-13.4324930899506</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.138887529232933</v>
       </c>
       <c r="E74">
-        <v>-12.72904890860214</v>
+        <v>-23.09465345657546</v>
       </c>
       <c r="F74">
-        <v>-0.8826943694248134</v>
+        <v>-3.944598740801459</v>
       </c>
       <c r="G74">
-        <v>-4.220883558169172</v>
+        <v>-13.64711779215388</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.213665820711351</v>
       </c>
       <c r="E75">
-        <v>-12.64023647636371</v>
+        <v>-24.61263417173863</v>
       </c>
       <c r="F75">
-        <v>-1.081563845284502</v>
+        <v>-3.955114036612597</v>
       </c>
       <c r="G75">
-        <v>-3.925383306968699</v>
+        <v>-11.09143994393358</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.247536642646947</v>
       </c>
       <c r="E76">
-        <v>-13.55356628507471</v>
+        <v>-25.84314282842087</v>
       </c>
       <c r="F76">
-        <v>-1.098754125627397</v>
+        <v>-4.518657350941517</v>
       </c>
       <c r="G76">
-        <v>-4.065311000371219</v>
+        <v>-11.10116876585733</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.245357971423241</v>
       </c>
       <c r="E77">
-        <v>-12.9529004357493</v>
+        <v>-26.68207886613387</v>
       </c>
       <c r="F77">
-        <v>-1.650914015107047</v>
+        <v>-5.20514695519394</v>
       </c>
       <c r="G77">
-        <v>-3.718823847358536</v>
+        <v>-12.36599764648429</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.204517660827516</v>
       </c>
       <c r="E78">
-        <v>-13.71807216035135</v>
+        <v>-25.83649502857762</v>
       </c>
       <c r="F78">
-        <v>-1.400319621881752</v>
+        <v>-3.746318234165162</v>
       </c>
       <c r="G78">
-        <v>-3.08818290729794</v>
+        <v>-14.44585571270483</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.132735776818251</v>
       </c>
       <c r="E79">
-        <v>-13.47802228167876</v>
+        <v>-26.9432857753703</v>
       </c>
       <c r="F79">
-        <v>-1.416999627904522</v>
+        <v>-4.310363539140178</v>
       </c>
       <c r="G79">
-        <v>-2.773746726477912</v>
+        <v>-13.73819465897939</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.029744084600464</v>
       </c>
       <c r="E80">
-        <v>-14.99708530212975</v>
+        <v>-26.89601756367824</v>
       </c>
       <c r="F80">
-        <v>-1.725766950358816</v>
+        <v>-4.766076611911882</v>
       </c>
       <c r="G80">
-        <v>-3.519007298053031</v>
+        <v>-13.94387803243318</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.904990743707393</v>
       </c>
       <c r="E81">
-        <v>-15.01660302510281</v>
+        <v>-27.5873344056892</v>
       </c>
       <c r="F81">
-        <v>-1.798970606111611</v>
+        <v>-4.616683864286602</v>
       </c>
       <c r="G81">
-        <v>-2.604908189915125</v>
+        <v>-12.16303440570327</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.758376236220998</v>
       </c>
       <c r="E82">
-        <v>-15.93843730800022</v>
+        <v>-28.11482917199867</v>
       </c>
       <c r="F82">
-        <v>-1.650682900601666</v>
+        <v>-5.00375592896013</v>
       </c>
       <c r="G82">
-        <v>-3.176848076277255</v>
+        <v>-11.45501241760629</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.598279325403152</v>
       </c>
       <c r="E83">
-        <v>-16.89663523717923</v>
+        <v>-29.84351525426473</v>
       </c>
       <c r="F83">
-        <v>-1.704459684024007</v>
+        <v>-5.379791654726159</v>
       </c>
       <c r="G83">
-        <v>-3.199721471768144</v>
+        <v>-10.08322883902768</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.422133874516136</v>
       </c>
       <c r="E84">
-        <v>-17.79183303596352</v>
+        <v>-28.93777516799058</v>
       </c>
       <c r="F84">
-        <v>-1.984408104534905</v>
+        <v>-5.210416200243148</v>
       </c>
       <c r="G84">
-        <v>-2.420720098897255</v>
+        <v>-11.07401009500981</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.235971502751691</v>
       </c>
       <c r="E85">
-        <v>-19.14907556622442</v>
+        <v>-29.88865508317319</v>
       </c>
       <c r="F85">
-        <v>-2.116810208361364</v>
+        <v>-4.584375050475213</v>
       </c>
       <c r="G85">
-        <v>-1.068433538824864</v>
+        <v>-10.11259905320627</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.035957930539897</v>
       </c>
       <c r="E86">
-        <v>-19.76626581720382</v>
+        <v>-32.33679341645986</v>
       </c>
       <c r="F86">
-        <v>-2.280400344903225</v>
+        <v>-5.10681146080761</v>
       </c>
       <c r="G86">
-        <v>-1.528398458249383</v>
+        <v>-9.014951692254586</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.829324236547095</v>
       </c>
       <c r="E87">
-        <v>-21.0028743283744</v>
+        <v>-30.3538878603512</v>
       </c>
       <c r="F87">
-        <v>-2.147938598623764</v>
+        <v>-4.729497564139061</v>
       </c>
       <c r="G87">
-        <v>-1.737287585166753</v>
+        <v>-10.72024519257828</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.61374074818982</v>
       </c>
       <c r="E88">
-        <v>-22.77499753332203</v>
+        <v>-32.93982086498027</v>
       </c>
       <c r="F88">
-        <v>-2.446056429747667</v>
+        <v>-5.196405193992197</v>
       </c>
       <c r="G88">
-        <v>-1.502043686683924</v>
+        <v>-10.65151016335103</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.39916700468604</v>
       </c>
       <c r="E89">
-        <v>-23.6610297007148</v>
+        <v>-32.49198195646572</v>
       </c>
       <c r="F89">
-        <v>-2.310783204503105</v>
+        <v>-5.205016073144297</v>
       </c>
       <c r="G89">
-        <v>-1.078290328389436</v>
+        <v>-9.48618104529268</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.185702468377379</v>
       </c>
       <c r="E90">
-        <v>-24.9858574140288</v>
+        <v>-35.08860442398989</v>
       </c>
       <c r="F90">
-        <v>-2.557449479504325</v>
+        <v>-5.197348704463986</v>
       </c>
       <c r="G90">
-        <v>-0.9141340949919761</v>
+        <v>-10.75621066209135</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.98669046682652</v>
       </c>
       <c r="E91">
-        <v>-26.86425937546245</v>
+        <v>-35.86107831292932</v>
       </c>
       <c r="F91">
-        <v>-2.681041067634609</v>
+        <v>-4.750759270266716</v>
       </c>
       <c r="G91">
-        <v>-0.9644319402767041</v>
+        <v>-9.801312845083311</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.803831230589998</v>
       </c>
       <c r="E92">
-        <v>-28.90847141268695</v>
+        <v>-36.01879147719445</v>
       </c>
       <c r="F92">
-        <v>-3.081785336291342</v>
+        <v>-5.027745448945203</v>
       </c>
       <c r="G92">
-        <v>-1.325126782641783</v>
+        <v>-10.83571137925514</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.651656129887567</v>
       </c>
       <c r="E93">
-        <v>-31.69031073136184</v>
+        <v>-39.09835531950364</v>
       </c>
       <c r="F93">
-        <v>-3.045642838139797</v>
+        <v>-3.774032093993222</v>
       </c>
       <c r="G93">
-        <v>-1.123505561478584</v>
+        <v>-11.33577938857919</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.530441170312747</v>
       </c>
       <c r="E94">
-        <v>-32.88879628409885</v>
+        <v>-41.09831058025117</v>
       </c>
       <c r="F94">
-        <v>-3.015258321805111</v>
+        <v>-5.294169943237997</v>
       </c>
       <c r="G94">
-        <v>-1.34748174512628</v>
+        <v>-10.5458154544782</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.451217691465756</v>
       </c>
       <c r="E95">
-        <v>-35.66224660467454</v>
+        <v>-40.82558549737623</v>
       </c>
       <c r="F95">
-        <v>-3.326459387688829</v>
+        <v>-5.490258589726488</v>
       </c>
       <c r="G95">
-        <v>-1.137962623669497</v>
+        <v>-10.662354600605</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.408473140045963</v>
       </c>
       <c r="E96">
-        <v>-37.87481372008219</v>
+        <v>-43.61217292104817</v>
       </c>
       <c r="F96">
-        <v>-3.241355405827417</v>
+        <v>-5.608719270163832</v>
       </c>
       <c r="G96">
-        <v>-1.93218558335465</v>
+        <v>-10.13658806402737</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.405255709907276</v>
       </c>
       <c r="E97">
-        <v>-39.78688941423688</v>
+        <v>-46.63341454661256</v>
       </c>
       <c r="F97">
-        <v>-3.631845314404895</v>
+        <v>-5.941587113835173</v>
       </c>
       <c r="G97">
-        <v>-2.276802440078451</v>
+        <v>-12.00833793406169</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.428844897254644</v>
       </c>
       <c r="E98">
-        <v>-41.93798023075341</v>
+        <v>-47.0307609699416</v>
       </c>
       <c r="F98">
-        <v>-3.622587480311208</v>
+        <v>-6.012767068022929</v>
       </c>
       <c r="G98">
-        <v>-2.785021003756164</v>
+        <v>-11.92708504458516</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.474545921639748</v>
       </c>
       <c r="E99">
-        <v>-44.49163427265581</v>
+        <v>-48.15301192699647</v>
       </c>
       <c r="F99">
-        <v>-3.678083126094358</v>
+        <v>-5.992803413615461</v>
       </c>
       <c r="G99">
-        <v>-2.394421108098306</v>
+        <v>-11.86553917179466</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.524853640658384</v>
       </c>
       <c r="E100">
-        <v>-46.00800285107224</v>
+        <v>-51.41257242204404</v>
       </c>
       <c r="F100">
-        <v>-3.446208179437526</v>
+        <v>-5.657356033851801</v>
       </c>
       <c r="G100">
-        <v>-3.181051321094904</v>
+        <v>-10.74720042768912</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.569309027396945</v>
       </c>
       <c r="E101">
-        <v>-48.44310710404633</v>
+        <v>-51.86556360186081</v>
       </c>
       <c r="F101">
-        <v>-3.804915287504393</v>
+        <v>-6.649902956600259</v>
       </c>
       <c r="G101">
-        <v>-3.553027003181354</v>
+        <v>-11.2323060667021</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.589391498574503</v>
       </c>
       <c r="E102">
-        <v>-51.09226326641499</v>
+        <v>-54.41822590795553</v>
       </c>
       <c r="F102">
-        <v>-3.545976749430698</v>
+        <v>-6.263966169452268</v>
       </c>
       <c r="G102">
-        <v>-3.565968141011804</v>
+        <v>-12.13821524582763</v>
       </c>
     </row>
   </sheetData>
